--- a/data/trans_camb/IQ2601_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IQ2601_R2-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-20,15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,58</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-12,28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-10,7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-20,15</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,06</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,48</t>
+          <t>8,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 0,25</t>
+          <t>-31,5; -7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 1,35</t>
+          <t>-7,7; 13,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 19,29</t>
+          <t>-4,81; 26,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-31,56; -8,27</t>
+          <t>-24,45; -0,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 13,34</t>
+          <t>-22,85; 0,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 25,04</t>
+          <t>-10,59; 18,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,42; -7,01</t>
+          <t>-25,32; -8,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 4,83</t>
+          <t>-11,58; 4,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 18,99</t>
+          <t>-3,5; 18,44</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-30,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-17,66%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-15,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-30,08%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,63; -0,06</t>
+          <t>-44,04; -12,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 2,09</t>
+          <t>-10,83; 21,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 29,01</t>
+          <t>-6,84; 42,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,16; -13,69</t>
+          <t>-32,95; -2,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 21,8</t>
+          <t>-31,46; 1,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 39,4</t>
+          <t>-14,35; 28,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,65; -10,94</t>
+          <t>-34,76; -12,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 7,66</t>
+          <t>-15,84; 7,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 29,06</t>
+          <t>-4,73; 28,27</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-20,06</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-14,4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,54</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-9,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-7,68</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-14,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-20,06</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-14,4</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>-15,0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,46</t>
+          <t>-6,15</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 2,84</t>
+          <t>-30,94; -7,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 2,88</t>
+          <t>-24,34; -2,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,42; 1,2</t>
+          <t>-15,57; 19,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,97; -8,85</t>
+          <t>-19,79; 3,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,35; -3,05</t>
+          <t>-17,35; 3,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 19,04</t>
+          <t>-32,79; 2,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,59; -7,57</t>
+          <t>-22,52; -6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -4,24</t>
+          <t>-18,59; -3,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 5,62</t>
+          <t>-19,87; 4,61</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-27,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-19,64%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-11,9%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-10,1%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-18,97%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-27,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-19,64%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>-19,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-8,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 4,06</t>
+          <t>-40,35; -11,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 3,82</t>
+          <t>-32,06; -4,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 1,59</t>
+          <t>-20,1; 28,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,89; -12,56</t>
+          <t>-24,6; 4,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,61; -4,6</t>
+          <t>-21,58; 5,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 27,59</t>
+          <t>-41,3; 3,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,99; -10,51</t>
+          <t>-28,88; -9,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,15; -5,98</t>
+          <t>-24,0; -5,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 7,68</t>
+          <t>-26,43; 6,29</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-13,14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,57</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-13,83</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-16,46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,56</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,65</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-13,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,57</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-15,71</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,36</t>
+          <t>-10,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,44; -3,65</t>
+          <t>-26,31; -0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 6,1</t>
+          <t>-2,55; 20,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 20,72</t>
+          <t>-35,77; 9,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,07; -0,86</t>
+          <t>-30,24; -2,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 20,27</t>
+          <t>-22,81; 4,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 4,56</t>
+          <t>-31,09; 18,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,87; -5,5</t>
+          <t>-22,38; -5,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 10,12</t>
+          <t>-7,89; 10,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 5,44</t>
+          <t>-27,43; 7,14</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-21,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-22,23%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-25,19%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-14,63%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-7,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-21,13%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-25,26%</t>
+          <t>-7,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-17,9%</t>
+          <t>-15,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -5,44</t>
+          <t>-38,83; -1,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 10,09</t>
+          <t>-3,64; 36,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,85; 33,82</t>
+          <t>-56,66; 13,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,43; -1,49</t>
+          <t>-42,0; -4,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 35,77</t>
+          <t>-31,7; 7,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 7,87</t>
+          <t>-46,21; 30,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,98; -9,89</t>
+          <t>-33,65; -9,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 17,07</t>
+          <t>-11,74; 18,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 8,37</t>
+          <t>-42,73; 11,03</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-13,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13,51</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-20,55</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-13,6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>7,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>10,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-27,85; -11,24</t>
+          <t>-21,45; -5,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 1,35</t>
+          <t>-4,18; 11,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 21,12</t>
+          <t>-0,72; 26,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -5,43</t>
+          <t>-27,81; -12,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 10,75</t>
+          <t>-12,97; 1,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 26,04</t>
+          <t>-7,22; 18,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -12,01</t>
+          <t>-23,11; -11,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 4,16</t>
+          <t>-6,41; 3,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 20,44</t>
+          <t>0,85; 19,21</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-21,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-29,24%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-8,81%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-21,87%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,01; -17,87</t>
+          <t>-32,55; -9,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 1,97</t>
+          <t>-6,38; 19,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 30,88</t>
+          <t>-1,01; 44,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,04; -9,43</t>
+          <t>-37,68; -17,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 18,24</t>
+          <t>-17,9; 1,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 43,32</t>
+          <t>-8,89; 27,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,12; -18,47</t>
+          <t>-33,75; -18,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 6,56</t>
+          <t>-9,2; 5,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 32,37</t>
+          <t>1,45; 29,77</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-12,06</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,8</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13,22</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-19,2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,41</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-12,06</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,8</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>10,73</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,55</t>
+          <t>11,86</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,8; -9,26</t>
+          <t>-21,57; -2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 4,86</t>
+          <t>-12,3; 7,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 25,96</t>
+          <t>-1,21; 24,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -2,65</t>
+          <t>-29,49; -9,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 7,27</t>
+          <t>-13,81; 5,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 24,21</t>
+          <t>-8,0; 23,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-23,03; -7,73</t>
+          <t>-22,2; -7,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 3,3</t>
+          <t>-10,1; 3,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 21,59</t>
+          <t>1,2; 20,85</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-18,65%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-2,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20,45%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-27,71%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-6,36%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-18,65%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-2,78%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,07; -13,8</t>
+          <t>-31,32; -4,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 8,26</t>
+          <t>-17,36; 12,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 40,8</t>
+          <t>-1,52; 41,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,86; -4,34</t>
+          <t>-39,41; -14,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 12,15</t>
+          <t>-18,62; 9,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 39,89</t>
+          <t>-9,72; 35,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,76; -12,5</t>
+          <t>-31,87; -13,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 5,19</t>
+          <t>-14,74; 6,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3,33; 34,46</t>
+          <t>2,12; 32,76</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-21,43</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,82</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>11,39</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-1,07</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>14,91</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-23,22</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-21,43</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,3</t>
+          <t>-20,94</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,9</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 14,55</t>
+          <t>-34,86; -8,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,93; 29,5</t>
+          <t>-18,02; 9,37</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-41,92; -1,37</t>
+          <t>-10,62; 27,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-33,49; -7,63</t>
+          <t>-14,95; 14,19</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 8,69</t>
+          <t>0,97; 28,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 29,82</t>
+          <t>-39,36; 3,56</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-21,01; -1,59</t>
+          <t>-21,26; -1,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 15,31</t>
+          <t>-3,7; 16,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 18,72</t>
+          <t>-16,42; 15,63</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-34,69%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-7,81%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-2,25%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>31,22%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-48,62%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-34,69%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-7,81%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>-43,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 35,18</t>
+          <t>-51,82; -13,98</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,73; 67,77</t>
+          <t>-26,18; 16,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,41; -3,38</t>
+          <t>-14,91; 47,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -13,65</t>
+          <t>-27,89; 32,8</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 15,61</t>
+          <t>1,67; 68,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 54,09</t>
+          <t>-77,82; 8,71</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -2,81</t>
+          <t>-36,12; -2,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 31,2</t>
+          <t>-6,47; 33,19</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 37,37</t>
+          <t>-28,23; 30,0</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-15,7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9,5</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-14,74</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-4,2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-15,7</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -10,29</t>
+          <t>-19,77; -11,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -0,02</t>
+          <t>-4,05; 3,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 9,31</t>
+          <t>2,89; 16,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -11,38</t>
+          <t>-19,3; -10,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 3,91</t>
+          <t>-8,4; 0,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,86; 15,16</t>
+          <t>-7,7; 6,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-18,34; -11,97</t>
+          <t>-18,04; -12,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,61</t>
+          <t>-5,13; 0,83</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,36; 10,57</t>
+          <t>0,5; 10,05</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-24,25%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-0,32%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-21,82%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-6,21%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-24,25%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-0,32%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,26; -15,76</t>
+          <t>-29,71; -17,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 0,03</t>
+          <t>-6,09; 6,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 14,02</t>
+          <t>4,37; 25,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,82; -18,25</t>
+          <t>-27,91; -15,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 6,35</t>
+          <t>-12,04; 0,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,27; 23,91</t>
+          <t>-11,21; 10,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,29; -18,71</t>
+          <t>-26,82; -18,87</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,93</t>
+          <t>-7,6; 1,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,98; 16,24</t>
+          <t>0,53; 15,34</t>
         </is>
       </c>
     </row>
